--- a/mosip_master/xlsx/screen_detail.xlsx
+++ b/mosip_master/xlsx/screen_detail.xlsx
@@ -1,20 +1,23 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28429"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\tf_nira\mosip-data\mosip_master\xlsx\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\NIRA-DEV\mosip-data\mosip_master\xlsx\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C9BDCC9-0021-44FC-B625-3F71B4FEF20B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAB483E5-A514-4D3F-AE44-B95B638D8EC8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11040" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="20730" windowHeight="11160" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">Sheet1!$A$1:$F$1</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
   <extLst>
     <ext xmlns:loext="http://schemas.libreoffice.org/" uri="{7626C862-2A13-11E5-B345-FEFF819CDC9F}">
@@ -25,7 +28,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="96" uniqueCount="27">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="101" uniqueCount="28">
   <si>
     <t>lang_code</t>
   </si>
@@ -106,6 +109,9 @@
   </si>
   <si>
     <t>getFirstIdRoot</t>
+  </si>
+  <si>
+    <t>renewUINRoot</t>
   </si>
 </sst>
 </file>
@@ -162,7 +168,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -171,6 +177,7 @@
     <xf numFmtId="49" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
+    <xf numFmtId="47" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -479,12 +486,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:F19"/>
+  <dimension ref="A1:I22"/>
   <sheetFormatPr defaultColWidth="8.42578125" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.85546875" customWidth="1"/>
     <col min="2" max="2" width="25.7109375" customWidth="1"/>
-    <col min="3" max="3" width="8.42578125" style="1"/>
+    <col min="3" max="3" width="34.5703125" style="1" customWidth="1"/>
     <col min="4" max="4" width="24.85546875" customWidth="1"/>
     <col min="5" max="5" width="23.42578125" customWidth="1"/>
     <col min="6" max="6" width="8.42578125" style="1"/>
@@ -535,16 +542,16 @@
         <v>6</v>
       </c>
       <c r="B3" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="C3" s="1">
         <v>10003</v>
       </c>
       <c r="D3" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="E3" t="s">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="F3" s="1" t="s">
         <v>8</v>
@@ -555,16 +562,16 @@
         <v>6</v>
       </c>
       <c r="B4" t="s">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="C4" s="1">
         <v>10003</v>
       </c>
       <c r="D4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="E4" t="s">
-        <v>10</v>
+        <v>22</v>
       </c>
       <c r="F4" s="1" t="s">
         <v>8</v>
@@ -575,16 +582,16 @@
         <v>6</v>
       </c>
       <c r="B5" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="C5" s="1">
         <v>10003</v>
       </c>
       <c r="D5" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="E5" t="s">
-        <v>11</v>
+        <v>26</v>
       </c>
       <c r="F5" s="1" t="s">
         <v>8</v>
@@ -595,16 +602,16 @@
         <v>6</v>
       </c>
       <c r="B6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="C6" s="1">
         <v>10003</v>
       </c>
       <c r="D6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="E6" t="s">
-        <v>12</v>
+        <v>9</v>
       </c>
       <c r="F6" s="1" t="s">
         <v>8</v>
@@ -615,16 +622,16 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="C7" s="1">
         <v>10003</v>
       </c>
       <c r="D7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="E7" t="s">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="F7" s="1" t="s">
         <v>8</v>
@@ -635,16 +642,16 @@
         <v>6</v>
       </c>
       <c r="B8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="C8" s="1">
         <v>10003</v>
       </c>
       <c r="D8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="E8" t="s">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="F8" s="1" t="s">
         <v>8</v>
@@ -655,16 +662,16 @@
         <v>6</v>
       </c>
       <c r="B9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="C9" s="1">
         <v>10003</v>
       </c>
       <c r="D9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="E9" t="s">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="F9" s="1" t="s">
         <v>8</v>
@@ -675,16 +682,16 @@
         <v>6</v>
       </c>
       <c r="B10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="C10" s="1">
         <v>10003</v>
       </c>
       <c r="D10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="E10" t="s">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="F10" s="1" t="s">
         <v>8</v>
@@ -695,16 +702,16 @@
         <v>6</v>
       </c>
       <c r="B11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="C11" s="1">
         <v>10003</v>
       </c>
       <c r="D11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="E11" t="s">
-        <v>17</v>
+        <v>19</v>
       </c>
       <c r="F11" s="1" t="s">
         <v>8</v>
@@ -715,16 +722,16 @@
         <v>6</v>
       </c>
       <c r="B12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C12" s="1">
         <v>10003</v>
       </c>
       <c r="D12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="E12" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="F12" s="1" t="s">
         <v>8</v>
@@ -735,16 +742,16 @@
         <v>6</v>
       </c>
       <c r="B13" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="C13" s="1">
         <v>10003</v>
       </c>
       <c r="D13" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="E13" t="s">
-        <v>19</v>
+        <v>14</v>
       </c>
       <c r="F13" s="1" t="s">
         <v>8</v>
@@ -775,16 +782,16 @@
         <v>6</v>
       </c>
       <c r="B15" t="s">
-        <v>21</v>
+        <v>15</v>
       </c>
       <c r="C15" s="1">
         <v>10003</v>
       </c>
       <c r="D15" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="E15" t="s">
-        <v>22</v>
+        <v>15</v>
       </c>
       <c r="F15" s="1" t="s">
         <v>8</v>
@@ -795,80 +802,103 @@
         <v>6</v>
       </c>
       <c r="B16" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="C16" s="1">
         <v>10003</v>
       </c>
       <c r="D16" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="E16" t="s">
-        <v>23</v>
+        <v>16</v>
       </c>
       <c r="F16" s="1" t="s">
         <v>8</v>
       </c>
     </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>6</v>
       </c>
       <c r="B17" t="s">
+        <v>17</v>
+      </c>
+      <c r="C17" s="1">
+        <v>10003</v>
+      </c>
+      <c r="D17" t="s">
+        <v>17</v>
+      </c>
+      <c r="E17" t="s">
+        <v>17</v>
+      </c>
+      <c r="F17" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="18" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A18" t="s">
+        <v>6</v>
+      </c>
+      <c r="B18" t="s">
+        <v>18</v>
+      </c>
+      <c r="C18" s="1">
+        <v>10003</v>
+      </c>
+      <c r="D18" t="s">
+        <v>18</v>
+      </c>
+      <c r="E18" t="s">
+        <v>18</v>
+      </c>
+      <c r="F18" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="19" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A19" t="s">
+        <v>6</v>
+      </c>
+      <c r="B19" t="s">
         <v>24</v>
       </c>
-      <c r="C17" s="1">
-        <v>10003</v>
-      </c>
-      <c r="D17" t="s">
+      <c r="C19" s="1">
+        <v>10003</v>
+      </c>
+      <c r="D19" t="s">
         <v>24</v>
       </c>
-      <c r="E17" t="s">
+      <c r="E19" t="s">
         <v>24</v>
       </c>
-      <c r="F17" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A18" t="s">
-        <v>6</v>
-      </c>
-      <c r="B18" t="s">
-        <v>25</v>
-      </c>
-      <c r="C18" s="1">
-        <v>10003</v>
-      </c>
-      <c r="D18" t="s">
-        <v>25</v>
-      </c>
-      <c r="E18" t="s">
-        <v>25</v>
-      </c>
-      <c r="F18" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="A19" t="s">
-        <v>6</v>
-      </c>
-      <c r="B19" t="s">
-        <v>26</v>
-      </c>
-      <c r="C19" s="1">
-        <v>10003</v>
-      </c>
-      <c r="D19" t="s">
-        <v>26</v>
-      </c>
-      <c r="E19" t="s">
-        <v>26</v>
-      </c>
       <c r="F19" s="1" t="s">
         <v>8</v>
       </c>
+    </row>
+    <row r="20" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="A20" s="1" t="s">
+        <v>6</v>
+      </c>
+      <c r="B20" t="s">
+        <v>27</v>
+      </c>
+      <c r="C20" s="1">
+        <v>10003</v>
+      </c>
+      <c r="D20" t="s">
+        <v>27</v>
+      </c>
+      <c r="E20" t="s">
+        <v>27</v>
+      </c>
+      <c r="F20" s="1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="22" spans="1:9" x14ac:dyDescent="0.25">
+      <c r="I22" s="4"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.51180555555555496" footer="0.51180555555555496"/>
